--- a/output/pdf_financials_xlsx/RBZ.xlsx
+++ b/output/pdf_financials_xlsx/RBZ.xlsx
@@ -3214,13 +3214,13 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.368377</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.439896</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.318753</v>
       </c>
     </row>
     <row r="93">
@@ -5051,7 +5051,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -5463,7 +5467,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -5977,7 +5985,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RBZ.xlsx
+++ b/output/pdf_financials_xlsx/RBZ.xlsx
@@ -1399,28 +1399,26 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.062476</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.148382</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.084594</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.4494</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.631778</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.001416</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003572</v>
       </c>
     </row>
     <row r="35">
@@ -1459,28 +1457,26 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.062476</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.148382</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.084594</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.4494</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.631778</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.001416</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003572</v>
       </c>
     </row>
     <row r="37">
@@ -1831,16 +1827,16 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.4544</v>
+        <v>0.005</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.641651</v>
+        <v>0.009873</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.045195</v>
+        <v>0.043779</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.018152</v>
+        <v>0.01458</v>
       </c>
     </row>
     <row r="49">
@@ -4555,7 +4551,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6236,7 +6232,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">

--- a/output/pdf_financials_xlsx/RBZ.xlsx
+++ b/output/pdf_financials_xlsx/RBZ.xlsx
@@ -604,10 +604,10 @@
         <v>0.067623</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.193972</v>
+        <v>0.216772</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.050589</v>
+        <v>0.087589</v>
       </c>
     </row>
     <row r="8">
@@ -9857,7 +9857,11 @@
           <t>Directors’ fees 10</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -11136,7 +11140,11 @@
           <t>Director fees 8</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
